--- a/example.xlsx
+++ b/example.xlsx
@@ -37,12 +37,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -55,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -77,28 +82,77 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -466,12 +520,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,312 +536,414 @@
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>the ticker, eg klic. claude reads this cell first</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>the ticker, eg klic. claude reads this cell first. row 1 is also the header row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>as of</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>company name from the sec ticker list</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>company name, lowercase. spread across b and c</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>cik</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>the sec id number for the company</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>sec ticker list</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>fiscal year end</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>month and day their fiscal year ends, eg 10/03. 52/53 week years land on a nearby saturday</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>sec filing index</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>month and day their fiscal year ends, eg 10/3</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>52/53 week years land on a nearby saturday</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>snapshot from the last run, not live. a plain number, nothing refreshes on its own</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>plain number from the last run. nothing refreshes on its own</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>date of that run</t>
         </is>
       </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>googlefinance</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>snapshot, not live</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>shares out</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>shares outstanding in millions, from the cover page of the newest 10q or 10k. not the weighted average</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>the date on that cover page</t>
-        </is>
-      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>shares outstanding in millions, newest cover page. not the weighted average</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>date on that cover page</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>10q cover, linked</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>market cap</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>formula. price times shares out, $ millions</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cash and st investments</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>cash plus short term investments from the newest balance sheet</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>balance sheet date and the xbrl tags used</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>cash plus short term investments, newest balance sheet</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>balance sheet date</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>10q q2 26, linked</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>the split, eg cash 155.0 + st inv 197.6</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>debt</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>all borrowings, current plus long term. 0 if they have none. leases left out</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>balance sheet date, or no borrowings in the 10q</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>all borrowings, current plus long term. 0 if none</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>balance sheet date</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>10q q2 26, linked</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>whats in it and whats left out, eg term loan only, royalty financing not included</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ev</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>market cap minus cash plus debt. what you pay for the business itself</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>formula. market cap minus cash plus debt. what you pay for the business itself</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ev / sales ttm</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>ev over the last 4 quarters of revenue. good for cyclicals and companies with thin earnings</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>formula pointing at the model tab</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>formula. ev over the last 4 quarters of revenue. n/m when revenue is 0 or less</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>good for cyclicals and thin earnings</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>p/e ttm</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>market cap over the last 4 quarters of net income. junk when earnings are tiny or full of one offs</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>formula pointing at the model tab</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>formula. market cap over the last 4 quarters of net income. n/m when earnings are 0 or less</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>why its n/m or why its junk, eg ttm loss from a one off charge</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>backlog</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>orders not shipped yet, newest number. not revenue, can be cancelled</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>period and filing, quote in the cell note</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>orders not shipped yet, newest number. blank if they dont report it</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>10q, linked</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>not reported, if so</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2 or 3 lines on what they sell and to who, from item 1 of the 10k</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10k link</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2 or 3 lines on what they sell and to who, written right here across b to e. the cell note holds the source link and quotes</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>customers</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>who buys from them. biggest names and customer concentration if they disclose it</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>filing link, quote in the cell note</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>who buys from them, biggest names and concentration if disclosed. across b to e</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>end markets</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>what their customers use it for, eg auto, memory, ai, industrial</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>filing link</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>what customers use it for, eg auto, memory, ai. across b to e</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>products</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>main product lines by name</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>filing link</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>main product lines by name, lowercase. across b to e</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>competitors</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>who they lose deals to, from the competition part of the 10k</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>filing link</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>who they lose deals to, from the 10k competition section. across b to e</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>notes (mine)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>yours. claude never touches this</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>yours. claude never touches this. across b to e</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>real sheet widths</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>a 22, b 16, c 9, d 13, e 45. this example is wider so the explanations fit</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B14:E14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -796,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -817,7 +975,7 @@
           <t>their fiscal quarter, not the calendar one. eg q3 fy26. klics q4 ends in early october</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>q4. there is no 10q for q4, so this column gets worked out from the 10k</t>
         </is>
@@ -827,7 +985,7 @@
           <t>fiscal year, eg fy25. the year the 10k covers</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>proj. a quarter you project. claude never touches these columns</t>
         </is>
@@ -839,22 +997,22 @@
           <t>period end</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>last day of the quarter, from the 10q</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>last day of the fiscal year, same as the 10k</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>last day of the fiscal year, from the 10k</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
@@ -866,22 +1024,22 @@
           <t>weeks</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>usually 13. 14 means an extra week so year over year looks better than it is</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>the extra week in a 53 week year usually lands here</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>52 or 53</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
@@ -898,7 +1056,7 @@
           <t>quarter</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>derived quarter</t>
         </is>
@@ -908,7 +1066,7 @@
           <t>fiscal year</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>proj</t>
         </is>
@@ -920,706 +1078,724 @@
           <t>source</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>accession number of the 10q this quarter came from</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>the 10k accession, minus the q3 10q accession</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>accession number of the 10k</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>short label linked to the 10q, eg 10q q3 26. accession number in the cell note</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>says 10k minus q3, linked to the 10k</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>short label linked to the 10k, eg 10k fy25</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>your note on where the guess came from</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>sales booked in the quarter. from the 10q income statement</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>no 10q for q4. full year from the 10k minus the 9 month ytd</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>the 4 quarters added up, checked against the 10k</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>you fill these in. claude never touches them</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>revenue y/y</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>formula. this quarter over the same quarter last year, minus 1. empty if that quarter isnt in the sheet</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>formula. watch the weeks row, a 14 week q4 against a 13 week one flatters this</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>formula. this year over last year</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>formula, works once you fill in revenue</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>cogs</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>cost of goods sold, what it cost to make what they sold. 10q income statement</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>fy cogs minus 9 month ytd cogs</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>you fill in, or back into it from a gross margin guess</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>gross profit</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>revenue minus cogs, checked against the gross profit they reported</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>from the 10k, checked the same way</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>gross margin</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>formula. gross profit over revenue. quick read on pricing power</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>formula. an odd q4 margin is often a year end charge, check other operating items too</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>sga</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>selling, general and admin. 10q income statement. if they split it into sales and marketing plus g&amp;a, pull.py adds the two</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>r&amp;d</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>research and development. 10q income statement. empty if they dont report it</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>other operating items</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>gains, impairments, restructuring, anything not sga or r&amp;d. its the plug that makes operating income match what they reported. a big number here means a one off, go read the filing. negative is a gain, positive is a charge</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>same plug for q4. the 10k notes explain it</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>same plug for the full year</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>usually 0 unless you expect a charge</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>operating income</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>income from operations exactly as they reported it. 10q</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>operating margin</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>formula. operating income over revenue</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>interest and other</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>pretax income minus operating income. interest earned on cash, interest paid on debt, fx, investment gains</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>same math on the 10k numbers</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>pretax income</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>income before taxes. 10q</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>taxes</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>income tax expense. shown in parentheses when its a tax benefit</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>tax rate</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>formula. taxes over pretax income. junk when pretax is near 0</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>formula. 15% is a fine default</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>net income</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>bottom line, what belongs to shareholders. 10q. checked: pretax minus taxes should land here, a gap means minority interest or discontinued ops</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>fy minus 9 month ytd</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>diluted shares</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>weighted average diluted shares for the quarter, millions. 10q</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>approx. 4 times the fy weighted average, minus the q1 q2 q3 weighted averages. gets an approx note</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>weighted average diluted shares from the 10k</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>you fill in. buybacks shrink it, stock comp grows it</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>eps</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>diluted eps as reported. checked against net income over diluted shares</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>approx. q4 net income over approx q4 shares, not fy eps minus 9 month eps. gets an approx note</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>diluted eps from the 10k</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>net income over diluted shares</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>cfo</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>cash from operations. 10qs report cash flow year to date, so each quarter is that ytd minus the last one</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>fy cfo from the 10k minus the 9 month ytd</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>from the 10k cash flow statement</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>cash spent on property and equipment. year to date in the 10q, differenced the same way as cfo</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>fy capex minus the 9 month ytd</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>from the 10k cash flow statement</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>fcf</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>formula. cfo minus capex. cash the business actually throws off</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>backlog</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>orders not shipped yet. not revenue, can be cancelled. from the 10q text, quote in the cell note</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>year end backlog from the 10k text</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>year end backlog from the 10k text</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>leave empty</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>what they said the next quarters revenue would be, from the 8k press release. low and high plus the quote in the cell note</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>q4 guidance from the q3 8k press release</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>full year guidance if they give one</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>line your proj up against this</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>segments</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>header. one row per segment under it, from the segment note in the 10q. they have to add up to revenue</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>segment a</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>revenue for that segment in the quarter, quoted from the filing in the cell note</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>fy segment revenue from the 10k minus the 9 month ytd</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>from the 10k segment note</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>end markets</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>header. one row per end market under it, if they break it out. also adds up to revenue</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>end market a</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>revenue from that end market in the quarter, quoted from the filing</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>usually only in the 10k, so q4 is fy minus the 3 quarters</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>from the 10k</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>you fill in</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>real sheet widths</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>a 24, every period column 10. this example is wider so the explanations fit</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="5" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B38:E38"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1668,27 +1844,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>date the run happened</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>newest period in the sheet after the run, eg q3 fy26</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>plain words. new quarter added, what moved, anything that failed</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>accession numbers of every 10q, 10k and 8k used</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>short linked labels for every 10q, 10k and 8k used</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>each check and whether it came back ok, flag or fail</t>
         </is>

--- a/example.xlsx
+++ b/example.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="m/d/yy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +41,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +110,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
       <top style="thin">
         <color rgb="00D9D9D9"/>
       </top>
@@ -115,9 +123,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00D9D9D9"/>
       </top>
@@ -130,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,6 +148,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,10 +170,26 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,425 +557,410 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>Ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>the ticker, eg klic. claude reads this cell first. row 1 is also the header row</t>
+          <t>Ticker as typed, e.g. KLIC. Claude reads this cell first</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>as of</t>
+          <t>As of</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>company name, lowercase. spread across b and c</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
+          <t>Company name, styled the way the 10-K cover writes it</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cik</t>
+          <t>CIK</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>the sec id number for the company</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+          <t>The SEC's ID number for the company</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sec</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>fiscal year end</t>
+          <t>Fiscal year end</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>month and day their fiscal year ends, eg 10/3</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
+          <t>Month/day the fiscal year ends, e.g. 10/3</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52/53 week years land on a nearby saturday</t>
+          <t>52/53-week years end on a nearby Saturday</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>plain number from the last run. nothing refreshes on its own</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>date of that run</t>
+          <t>Price ($)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Snapshot from the last run. Nothing refreshes on its own</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Date of that run</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>googlefinance</t>
+          <t>GOOGLEFINANCE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>snapshot, not live</t>
+          <t>Snapshot, not live</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>shares out</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>shares outstanding in millions, newest cover page. not the weighted average</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>date on that cover page</t>
+          <t>Shares out (M)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Shares outstanding from the newest cover page. Not the weighted average</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Date on that cover page</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>10q cover, linked</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+          <t>10-Q Q3 FY26 cover (linked)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>market cap</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>formula. price times shares out, $ millions</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
+          <t>Market cap ($M)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Price × shares out</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cash and st investments</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>cash plus short term investments, newest balance sheet</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>balance sheet date</t>
+          <t>Cash and ST investments ($M)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Cash plus short-term investments, newest balance sheet</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Balance sheet date</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>10q q2 26, linked</t>
+          <t>10-Q Q3 FY26 (linked)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>the split, eg cash 155.0 + st inv 197.6</t>
+          <t>The split, e.g. Cash 368.6 + ST inv 148.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>debt</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>all borrowings, current plus long term. 0 if none</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>balance sheet date</t>
+          <t>Debt ($M)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>All borrowings, current plus long-term. 0 if none</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Balance sheet date</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>10q q2 26, linked</t>
+          <t>10-Q Q3 FY26 (linked)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>whats in it and whats left out, eg term loan only, royalty financing not included</t>
+          <t>What's in it and what's left out, e.g. Term loan only; royalty financing not included</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ev</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>formula. market cap minus cash plus debt. what you pay for the business itself</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
+          <t>EV ($M)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Market cap − cash + debt. What you pay for the business itself</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ev / sales ttm</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>formula. ev over the last 4 quarters of revenue. n/m when revenue is 0 or less</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>EV / Sales (TTM)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>EV over the last 4 quarters of revenue. NM if revenue ≤ 0</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>good for cyclicals and thin earnings</t>
+          <t>Useful for cyclicals and thin earnings</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>p/e ttm</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>formula. market cap over the last 4 quarters of net income. n/m when earnings are 0 or less</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Market cap over the last 4 quarters of net income. NM if earnings ≤ 0</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>why its n/m or why its junk, eg ttm loss from a one off charge</t>
+          <t>Why it's NM or distorted, e.g. TTM loss from a one-off charge</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>backlog</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>orders not shipped yet, newest number. blank if they dont report it</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>period</t>
+          <t>Backlog ($M)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Orders not yet shipped. Blank if not reported</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Period</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>10q, linked</t>
+          <t>10-Q (linked)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>not reported, if so</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>Say so if it isn't reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2 or 3 lines on what they sell and to who, written right here across b to e. the cell note holds the source link and quotes</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t>2–3 lines on what they sell and to whom, written right here. The cell note holds the source link and exact quotes</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>customers</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>who buys from them, biggest names and concentration if disclosed. across b to e</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>Who buys from them; biggest names and concentration if disclosed</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>end markets</t>
+          <t>End markets</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>what customers use it for, eg auto, memory, ai. across b to e</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t>What customers use it for, e.g. auto, memory, AI</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>products</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>main product lines by name, lowercase. across b to e</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Main product lines, styled the way the company writes them</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>competitors</t>
+          <t>Competitors</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>who they lose deals to, from the 10k competition section. across b to e</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>Who they compete with, from the 10-K competition section</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>notes (mine)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>yours. claude never touches this. across b to e</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>real sheet widths</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>a 22, b 16, c 9, d 13, e 45. this example is wider so the explanations fit</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="5" t="n"/>
+          <t>Notes (mine)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Yours. Claude never touches this</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B2:C2"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B19:E19"/>
@@ -954,848 +976,903 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>fiscal label</t>
+          <t>Fiscal label</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>their fiscal quarter, not the calendar one. eg q3 fy26. klics q4 ends in early october</t>
+          <t>Their fiscal quarter, e.g. Q3 FY26. Not the calendar quarter</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>q4. there is no 10q for q4, so this column gets worked out from the 10k</t>
+          <t>Q4 FY25. No 10-Q exists for Q4, so it's worked out from the 10-K</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>fiscal year, eg fy25. the year the 10k covers</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>proj. a quarter you project. claude never touches these columns</t>
+          <t>FY25, the year the 10-K covers</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Proj. Your projections; Claude never touches these</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>period end</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>last day of the quarter, from the 10q</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>last day of the fiscal year, same as the 10k</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>last day of the fiscal year, from the 10k</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>Period end</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Last day of the quarter (m/d/yy)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Last day of the fiscal year</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Last day of the fiscal year</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>weeks</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>usually 13. 14 means an extra week so year over year looks better than it is</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>the extra week in a 53 week year usually lands here</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+          <t>Weeks</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Usually 13. 14 means an extra week, which flatters year over year</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>The extra week of a 53-week year usually lands here</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>52 or 53</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
-        </is>
-      </c>
+      <c r="E3" s="16" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>quarter</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>derived quarter</t>
+          <t>Derived quarter</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>fiscal year</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>proj</t>
+          <t>Fiscal year</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Proj</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>short label linked to the 10q, eg 10q q3 26. accession number in the cell note</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>says 10k minus q3, linked to the 10k</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>short label linked to the 10k, eg 10k fy25</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>your note on where the guess came from</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Short label linked to the filing, e.g. 10-Q Q3 FY26. Accession number in the cell note</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>10-K FY25 less Q3, linked to the 10-K</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>10-K FY25, linked</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Your note on where the guess came from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>$M unless noted</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>sales booked in the quarter. from the 10q income statement</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>no 10q for q4. full year from the 10k minus the 9 month ytd</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>the 4 quarters added up, checked against the 10k</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>you fill these in. claude never touches them</t>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sales booked in the quarter, from the 10-Q income statement</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Full year from the 10-K minus the 9-month YTD</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>The 4 quarters added up, checked against the 10-K</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>You fill these in</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>revenue y/y</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Y/Y</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>formula. this quarter over the same quarter last year, minus 1. empty if that quarter isnt in the sheet</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>formula. watch the weeks row, a 14 week q4 against a 13 week one flatters this</t>
+          <t>Formula. This quarter over the same quarter last year. Blank if that quarter isn't in the sheet</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Formula. Check the Weeks row: 14 vs 13 weeks flatters this</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>formula. this year over last year</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>formula, works once you fill in revenue</t>
+          <t>Formula. This year over last year</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Formula, works once you fill in revenue</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>cogs</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>COGS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>cost of goods sold, what it cost to make what they sold. 10q income statement</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>fy cogs minus 9 month ytd cogs</t>
+          <t>Cost of goods sold, from the 10-Q</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>you fill in, or back into it from a gross margin guess</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>gross profit</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>revenue minus cogs, checked against the gross profit they reported</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>from the 10k, checked the same way</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Revenue − COGS, checked against reported gross profit</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>gross margin</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>formula. gross profit over revenue. quick read on pricing power</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>formula. an odd q4 margin is often a year end charge, check other operating items too</t>
+          <t>Formula. Gross profit / revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Formula. An odd Q4 margin is often a year-end charge</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>formula</t>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>sga</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>selling, general and admin. 10q income statement. if they split it into sales and marketing plus g&amp;a, pull.py adds the two</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
+          <t>Selling, general and admin. If they split it, sales &amp; marketing + G&amp;A</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>r&amp;d</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>research and development. 10q income statement. empty if they dont report it</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
+          <t>Research and development. Blank if not reported</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>other operating items</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Other operating items</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>gains, impairments, restructuring, anything not sga or r&amp;d. its the plug that makes operating income match what they reported. a big number here means a one off, go read the filing. negative is a gain, positive is a charge</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>same plug for q4. the 10k notes explain it</t>
+          <t>Gains, impairments, restructuring: anything that isn't SG&amp;A or R&amp;D. The plug that makes operating income match. Big number = one-off, read the filing</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Same plug for Q4</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>same plug for the full year</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>usually 0 unless you expect a charge</t>
+          <t>Same plug for the year</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Usually 0 unless you expect a charge</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>operating income</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>income from operations exactly as they reported it. 10q</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Exactly as reported in the 10-Q</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>operating margin</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Operating margin</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>formula. operating income over revenue</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>formula</t>
+          <t>Formula. Operating income / revenue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>formula</t>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>interest and other</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Interest and other</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>pretax income minus operating income. interest earned on cash, interest paid on debt, fx, investment gains</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
+          <t>Pretax income − operating income. Interest, FX, investment gains</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>same math on the 10k numbers</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>Same math on the 10-K</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>pretax income</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Pretax income</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>income before taxes. 10q</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
+          <t>Income before taxes, from the 10-Q</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>taxes</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>income tax expense. shown in parentheses when its a tax benefit</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
+          <t>Income tax expense. Parentheses = a tax benefit</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>tax rate</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>formula. taxes over pretax income. junk when pretax is near 0</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>formula</t>
+          <t>Formula. Taxes / pretax income. NM when pretax ≤ 0</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>formula. 15% is a fine default</t>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Formula. 15% is a fine default</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>net income</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>bottom line, what belongs to shareholders. 10q. checked: pretax minus taxes should land here, a gap means minority interest or discontinued ops</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>fy minus 9 month ytd</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Bottom line, as reported. Pretax − taxes should land here; a gap means minority interest or discontinued ops</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>FY minus 9-month YTD</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>diluted shares</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Diluted shares (M)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>weighted average diluted shares for the quarter, millions. 10q</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>approx. 4 times the fy weighted average, minus the q1 q2 q3 weighted averages. gets an approx note</t>
+          <t>Weighted average diluted shares for the quarter</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Approx: 4 × FY average − the Q1, Q2, Q3 averages. Gets an approx note</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>weighted average diluted shares from the 10k</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>you fill in. buybacks shrink it, stock comp grows it</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Buybacks shrink it, stock comp grows it</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>eps</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>EPS ($)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>diluted eps as reported. checked against net income over diluted shares</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>approx. q4 net income over approx q4 shares, not fy eps minus 9 month eps. gets an approx note</t>
+          <t>Diluted EPS as reported, checked against net income / shares</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Approx: Q4 net income / approx Q4 shares. Gets an approx note</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>diluted eps from the 10k</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>net income over diluted shares</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Net income / diluted shares</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>cfo</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CFO</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>cash from operations. 10qs report cash flow year to date, so each quarter is that ytd minus the last one</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>fy cfo from the 10k minus the 9 month ytd</t>
+          <t>Cash from operations. 10-Qs report YTD, so each quarter is YTD minus the prior YTD</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>FY from the 10-K minus the 9-month YTD</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>from the 10k cash flow statement</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K cash flow statement</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>capex</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Capex</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>cash spent on property and equipment. year to date in the 10q, differenced the same way as cfo</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>fy capex minus the 9 month ytd</t>
+          <t>Cash spent on property and equipment, differenced the same way</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>FY minus the 9-month YTD</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>from the 10k cash flow statement</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
+          <t>From the 10-K</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>You fill in</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>fcf</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>formula. cfo minus capex. cash the business actually throws off</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>formula</t>
+          <t>FCF</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Formula. CFO − capex</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>backlog</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>orders not shipped yet. not revenue, can be cancelled. from the 10q text, quote in the cell note</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>year end backlog from the 10k text</t>
+          <t>Orders not yet shipped. Not revenue; can be cancelled. Quote in the cell note</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Year-end backlog from the 10-K</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>year end backlog from the 10k text</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>leave empty</t>
+          <t>Year-end backlog from the 10-K</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Leave blank</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>guidance</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Guidance (next Q revenue)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>what they said the next quarters revenue would be, from the 8k press release. low and high plus the quote in the cell note</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>q4 guidance from the q3 8k press release</t>
+          <t>Next quarter's revenue guidance from the earnings 8-K. Midpoint here, low/high and quote in the note</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>From the Q3 8-K</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>full year guidance if they give one</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>line your proj up against this</t>
+          <t>Full-year guidance if given</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Line your projection up against this</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>segments</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>header. one row per segment under it, from the segment note in the 10q. they have to add up to revenue</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
+          <t>Segments</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>segment a</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Segment A</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>revenue for that segment in the quarter, quoted from the filing in the cell note</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>fy segment revenue from the 10k minus the 9 month ytd</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>from the 10k segment note</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
-        </is>
-      </c>
+          <t>One row per reported segment, from the segment note. They must add up to revenue</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>end markets</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>header. one row per end market under it, if they break it out. also adds up to revenue</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="11" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>end market a</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>revenue from that end market in the quarter, quoted from the filing</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>usually only in the 10k, so q4 is fy minus the 3 quarters</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>from the 10k</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>you fill in</t>
-        </is>
-      </c>
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="11" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>real sheet widths</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>a 24, every period column 10. this example is wider so the explanations fit</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="A38" s="3" t="n"/>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n"/>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>End markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>End market A</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>The revenue breakdown the company leads with (by product, end market or region). Adds up to revenue</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n"/>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>Real sheet</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>8 quarters (B–I), 3 fiscal years (J–L), 4 Proj (M–P). Column A 26 wide, the rest 10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B38:E38"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1809,64 +1886,64 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>run date</t>
+          <t>Run date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>latest period</t>
+          <t>Latest period</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>what changed</t>
+          <t>What changed</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>filings used</t>
+          <t>Filings used</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>checks passed or failed</t>
+          <t>Checks</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>date the run happened</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>newest period in the sheet after the run, eg q3 fy26</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>plain words. new quarter added, what moved, anything that failed</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>short linked labels for every 10q, 10k and 8k used</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>each check and whether it came back ok, flag or fail</t>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Newest period in the sheet, e.g. Q3 FY26</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Plain words: what was added, what moved, what failed</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Short linked labels for every 10-Q, 10-K and 8-K used</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Each check: OK, Flag or Fail</t>
         </is>
       </c>
     </row>
